--- a/rental_application_form_templates/046_vacation_rental_form--rental_application_form_templates.xlsx
+++ b/rental_application_form_templates/046_vacation_rental_form--rental_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday',_'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday', 'value': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday',_'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday', 'value': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday',_'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday', 'value': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday',_'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday', 'value': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday',_'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday', 'value': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'saturday',_'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Saturday', 'value': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'sunday',_'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Sunday', 'value': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1_week',_'value':_'1_week'}</t>
+          <t>1_week</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1 week', 'value': '1 week'}</t>
+          <t>1 week</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2_weeks',_'value':_'2_weeks'}</t>
+          <t>2_weeks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2 weeks', 'value': '2 weeks'}</t>
+          <t>2 weeks</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'3_weeks',_'value':_'3_weeks'}</t>
+          <t>3_weeks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '3 weeks', 'value': '3 weeks'}</t>
+          <t>3 weeks</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'4_weeks',_'value':_'4_weeks'}</t>
+          <t>4_weeks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '4 weeks', 'value': '4 weeks'}</t>
+          <t>4 weeks</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'5_weeks',_'value':_'5_weeks'}</t>
+          <t>5_weeks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '5 weeks', 'value': '5 weeks'}</t>
+          <t>5 weeks</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'6_weeks',_'value':_'6_weeks'}</t>
+          <t>6_weeks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': '6 weeks', 'value': '6 weeks'}</t>
+          <t>6 weeks</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'7_weeks',_'value':_'7_weeks'}</t>
+          <t>7_weeks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': '7 weeks', 'value': '7 weeks'}</t>
+          <t>7 weeks</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'8_weeks',_'value':_'8_weeks'}</t>
+          <t>8_weeks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': '8 weeks', 'value': '8 weeks'}</t>
+          <t>8 weeks</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'house',_'value':_'house'}</t>
+          <t>house</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'House', 'value': 'House'}</t>
+          <t>House</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'apartment',_'value':_'apartment'}</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Apartment', 'value': 'Apartment'}</t>
+          <t>Apartment</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'condo',_'value':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Condo', 'value': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'townhouse',_'value':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Townhouse', 'value': 'Townhouse'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
